--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:29</t>
+          <t>2026-08-30 13:48:24</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13:30:40</t>
+          <t>13:48:34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:40</t>
+          <t>2026-08-30 13:48:34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -703,12 +703,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13:30:26</t>
+          <t>13:48:20</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 13:30:27</t>
+          <t>2026-08-30 13:48:20</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">

--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 13:48:24</t>
+          <t>2026-08-30 15:45:24</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13:48:34</t>
+          <t>15:45:48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 13:48:34</t>
+          <t>2026-08-30 15:45:49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -703,12 +703,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13:48:20</t>
+          <t>15:45:21</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 13:48:20</t>
+          <t>2026-08-30 15:45:22</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">

--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 15:45:24</t>
+          <t>2026-08-30 16:40:22</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15:45:48</t>
+          <t>16:40:33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 15:45:49</t>
+          <t>2026-08-30 16:40:34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -703,12 +703,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15:45:21</t>
+          <t>16:40:19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 15:45:22</t>
+          <t>2026-08-30 16:40:19</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">

--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 16:40:22</t>
+          <t>2026-08-30 16:43:09</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16:40:33</t>
+          <t>16:43:25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 16:40:34</t>
+          <t>2026-08-30 16:43:25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -703,12 +703,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16:40:19</t>
+          <t>16:43:06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 16:40:19</t>
+          <t>2026-08-30 16:43:06</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">

--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 16:43:09</t>
+          <t>2026-08-30 17:27:03</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16:43:25</t>
+          <t>17:27:15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 16:43:25</t>
+          <t>2026-08-30 17:27:15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -703,12 +703,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16:43:06</t>
+          <t>17:27:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 16:43:06</t>
+          <t>2026-08-30 17:27:00</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">

--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 17:27:03</t>
+          <t>2026-08-30 17:39:43</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17:27:15</t>
+          <t>17:39:55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 17:27:15</t>
+          <t>2026-08-30 17:39:55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -703,12 +703,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17:27:00</t>
+          <t>17:39:40</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 17:27:00</t>
+          <t>2026-08-30 17:39:41</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">

--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 17:39:43</t>
+          <t>2026-08-30 17:51:55</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17:39:55</t>
+          <t>17:52:14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 17:39:55</t>
+          <t>2026-08-30 17:52:14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -703,12 +703,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17:39:40</t>
+          <t>17:51:53</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 17:39:41</t>
+          <t>2026-08-30 17:51:53</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">

--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -759,11 +759,11 @@
     </row>
     <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="n">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>dhilip11111</t>
+          <t>dhilip</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12:36:01</t>
+          <t>18:14:22</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 12:36:17</t>
+          <t>2026-08-30 18:14:35</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">

--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 17:51:55</t>
+          <t>2026-08-30 18:37:27</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>115</v>
+        <v>146</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -663,12 +663,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17:52:14</t>
+          <t>18:37:35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 17:52:14</t>
+          <t>2026-08-30 18:37:36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -703,12 +703,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17:51:53</t>
+          <t>18:37:24</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 17:51:53</t>
+          <t>2026-08-30 18:37:24</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">

--- a/data/private/admin_registry.xlsx
+++ b/data/private/admin_registry.xlsx
@@ -548,7 +548,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 18:37:27</t>
+          <t>2026-08-31 19:52:54</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -658,17 +658,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18:37:35</t>
+          <t>19:53:01</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 18:37:36</t>
+          <t>2026-08-31 19:53:01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -679,7 +679,7 @@
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -698,17 +698,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18:37:24</t>
+          <t>19:52:52</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-30 18:37:24</t>
+          <t>2026-08-31 19:52:52</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
